--- a/ig/nr-add-collaboration/all-profiles.xlsx
+++ b/ig/nr-add-collaboration/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:57:30+00:00</t>
+    <t>2023-05-31T07:48:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
